--- a/AAII_Financials/Quarterly/BIDU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIDU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>BIDU</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4611500</v>
+      </c>
+      <c r="E8" s="3">
         <v>4650300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4680900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4378900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4566400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4472100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4675100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4783900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4669300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4364400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4929000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4721000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4695900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4533900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4663200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4495700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4121500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3923000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4568800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4537600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4502500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4040600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4212600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4122700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3836400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3529600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4447600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4380800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4022100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3669600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3949500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3947300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3726500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2999700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3495800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3486000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3097900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2456400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2648600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2654500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2811500</v>
+      </c>
+      <c r="E9" s="3">
         <v>2840100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2613100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2572600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2562500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2409800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2468000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2337900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2256500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2117700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2420700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2233100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2229200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2205800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2388900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2248300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2109100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2146600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2387300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2292300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2283100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2154600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2021500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1871400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1935400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2299400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2389300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2555100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2462200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2257300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2267200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1990000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1723500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1420900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1698700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1751400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1570500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1342800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1413800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1346200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1810200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2067800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1806200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2004000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2062300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2207100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2446100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2412700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2246700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2508300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2487900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2466700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2328100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2274300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2247400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2012500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1776400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2181500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2245300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2219400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1886000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2191100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2251300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1900900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1230200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2058300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1825600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1559900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1412300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1682300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1957300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2003000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1578900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1797200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1734600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1527400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1113600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1234800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1308400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>678200</v>
+      </c>
+      <c r="E12" s="3">
         <v>635200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>799400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>727500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>714600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>626200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>755600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>765000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>810400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>742700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>886600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>836100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>879900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>789500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>797700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>795400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>874700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>774400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1020400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>876600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>902400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>732200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>789300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>666000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>713100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>695600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>732300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>731700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>723300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>633700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>657700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>548100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>578700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>472600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>549600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>481100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>467200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>412300</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>432100</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>380100</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,52 +1496,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2299100</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>430300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-406200</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>44900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>302400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-156000</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1541,8 +1561,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>16</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>16</v>
@@ -1559,11 +1579,11 @@
       <c r="AB14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD14" s="3">
         <v>123300</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>16</v>
@@ -1571,21 +1591,21 @@
       <c r="AF14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH14" s="3">
         <v>72600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-714800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-128100</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
@@ -1601,53 +1621,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>323600</v>
+      </c>
+      <c r="E15" s="3">
         <v>318700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1131800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>321100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>297900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>268700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1309200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>251500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>232700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>223900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>285900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>504500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>507600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>526400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4166300</v>
+      </c>
+      <c r="E17" s="3">
         <v>4187400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4468900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4224500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4109000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3850900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4138500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3939300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3851300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3604900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4132900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3861100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3977500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3808900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4015700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3761100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3648900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3563800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4298400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4209500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4005100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3640000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3519800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3223800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3299400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3598100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3854100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4013400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3986500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3812000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3860600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2612800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2820400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2344300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2787100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2788500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2473100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2164700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2330800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2249200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>445200</v>
+      </c>
+      <c r="E18" s="3">
         <v>462900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>212000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>154400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>457400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>621200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>536600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>844700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>818000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>759500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>796100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>859900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>718400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>725000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>647500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>734600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>472700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>359100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>270400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>328100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>497400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>692800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>899000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>537000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-68400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>593400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>367400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>35600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-142400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>88900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1334500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>906100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>655400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>708700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>697500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>624800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>291700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>317800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>405300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,225 +2085,229 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>396400</v>
+      </c>
+      <c r="E20" s="3">
         <v>101600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-115900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-503500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-361600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-608700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>196500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>66100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-33900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>271600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>63300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-32800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-216000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>355100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-559000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>124000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-310800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>176700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2930300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-227600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3533100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>182400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1409000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>174800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-45700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>334800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1356700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>312100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>242300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>147300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>614800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>45800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>351800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>106000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>727500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>163000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>71700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>382700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>372300</v>
+      </c>
+      <c r="E21" s="3">
         <v>680000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1333500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>591400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1258800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1251600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2454500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>899700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>984600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1017400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>810300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1301100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1258800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1467400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>998300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>191100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>604700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>265800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>472400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2657100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>284700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4165100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3715700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1083400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1903900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>167500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2932100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-981900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>347700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>327800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>880500</v>
-      </c>
-      <c r="AH21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>16</v>
@@ -2278,392 +2315,404 @@
       <c r="AJ21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL21" s="3">
         <v>1868400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1469900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>789600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>507400</v>
-      </c>
-      <c r="AO21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AP21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E22" s="3">
         <v>92200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>93100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>88600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>97900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>110400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>88100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>95900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>102100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>106100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>109200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>116900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>112700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>117000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>104000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>103000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>98000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>120500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>125100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>121400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>118200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>108200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>110300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>120800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>117600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>103800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>122900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>123000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>105400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>83400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>67000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>68600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>50500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>59500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>82700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>49600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>47000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>42800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>472300</v>
+      </c>
+      <c r="E23" s="3">
         <v>553700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>389700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1846400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1136300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1239600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>901100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1226000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>924100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>932100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>404000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1120900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>907200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1102700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>898600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>75600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>493700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-49700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>326600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2727300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>148400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3815400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>767000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2197800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>590900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-231700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>824400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1112200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>224700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>152800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1882300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>883300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>956700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>755200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1342400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>738200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>316400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>657700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>601800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E24" s="3">
         <v>76600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>147100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-256800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>123000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>162200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>221800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>116000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>155600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>122300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-13500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>175700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>175100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>173700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>176800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>125400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>54000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>178800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-261400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>315500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>220300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>142800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>236300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>180100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>31000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>145700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>63600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>44700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>70300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>287300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>155800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>160700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>137900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>162800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>83700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>58900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>58300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E26" s="3">
         <v>477100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>242600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1589600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1013300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1077400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>679300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1110000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>768400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>809800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>417600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>945200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>732000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>929100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>721800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-49900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>490200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-103700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>147700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2465900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-167200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3595100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>624200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1961500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>410800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-262700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>777600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1257900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>161200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-50200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>82500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1595000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>727400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>796000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>617300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1179600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>654500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>257500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>599400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>449800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>266500</v>
+      </c>
+      <c r="E27" s="3">
         <v>499500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>122400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1577700</v>
       </c>
-      <c r="G27" s="3">
-        <v>1022100</v>
-      </c>
       <c r="H27" s="3">
+        <v>964600</v>
+      </c>
+      <c r="I27" s="3">
         <v>1063500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>630800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1088000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>755200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>754500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>265400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>915600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>718400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>848000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>615000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>505600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-122200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>188500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2353900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-83700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3684300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>714400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1997400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>520600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>965100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-994300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>368500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-49700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>283300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1734900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>918600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>960500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>620000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1179700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>655200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>258400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>519400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>451200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-396400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-101600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>115900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>503500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>361600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>608700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-196500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-66100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>33900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-271600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-63300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>32800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>216000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-355100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>559000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-124000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>310800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-176700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2930300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>227600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3533100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-182400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1409000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-174800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>45700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-334800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1356700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-312100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-242300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-147300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-614800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-45800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-351800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-106000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-727500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-163000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-71700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-382700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-243000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>341400</v>
+      </c>
+      <c r="E33" s="3">
         <v>499500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>254800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1577700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1022100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1063500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>711300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1088000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>755200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>754500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>366500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>915600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>718400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>848000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>615000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>505600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-122200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>188500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2353900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-83700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3684300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>714400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1997400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>520600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>965100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-994300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>368500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-49700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>283300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1734900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>918600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>960500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>620000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1179700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>655200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>258400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>519400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>451200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>341400</v>
+      </c>
+      <c r="E35" s="3">
         <v>499500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>254800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1577700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1022100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1063500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>711300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1088000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>755200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>754500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>366500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>915600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>718400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>848000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>615000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>505600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-122200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>188500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2353900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-83700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3684300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>714400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1997400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>520600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>965100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-994300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>368500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-49700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>283300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1734900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>918600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>960500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>620000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1179700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>655200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>258400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>519400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>451200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,385 +4305,395 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3610300</v>
+      </c>
+      <c r="E41" s="3">
         <v>4341900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3518000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5424800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4179300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6780400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3402100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4089000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5990700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4212700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3558200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4784100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5799500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3441200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7493900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7621500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5912900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5085800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5088200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5785600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6160700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5966500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4980900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2690300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2998600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3406900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5149600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2272100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3165300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4927200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4013900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2207900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4140700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3016700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1645000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2279100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2298000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2118300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1585000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1669400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20864300</v>
+      </c>
+      <c r="E42" s="3">
         <v>12605000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12961900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12107400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13111200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12756400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14057600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14844800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14699700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>20743900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>23841300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21429000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20420400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23165300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17035900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16323300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18872400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>19769200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19779000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>20345500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18151700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17348400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>17595200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>18527700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>19477200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19400300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>17388000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>18757600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>17474100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>16590500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>16211400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>12416700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>14165100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>12831800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>15988400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>16952300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>15088300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>13405600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>11480700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>9726700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2577900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2167200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2399200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1758900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1720600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1629000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1956400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1600500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1721200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1676900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2343800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2148100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2265500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2330500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2419900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2011200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1535200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1460100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1567100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1371900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1445200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1326000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1307600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1219800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1229400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1516800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1387400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1216900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1260000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1096500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>987600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4027500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>810400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>743900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4256000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2937200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2097300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1317100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>909700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>659100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="3">
+        <v>1219800</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>886400</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>16</v>
@@ -4605,11 +4701,11 @@
       <c r="H44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3">
         <v>820500</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>16</v>
@@ -4617,11 +4713,11 @@
       <c r="L44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" s="3">
         <v>196900</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>16</v>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,618 +4803,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2229700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3315300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1929700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2891900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2890400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3031900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1293700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2340200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1755500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1880800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>806800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1656100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1498000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2792000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3057900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2908400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2805800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2889300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3020200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3115200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2956800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2880700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1637500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1387300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1647800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1553100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1568300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1905500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1825900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1398300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1311400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>939800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>6419600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7337700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>545700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>845200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>712700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>528100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>532600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>837800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30527000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22514100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21727400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22234800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21946200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24230600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23132900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24537500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25769700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30119500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32471900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31578700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31545000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>33367100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30007600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>28864400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>29126400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>29204300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>29454500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30618300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>28714500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>27521800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>25521200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>23825100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>25353000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>25877000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>25493200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>24152100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23725200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>24012400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>22524300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19591900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>25535700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>23930200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>22435000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>23013800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>20196200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>17369200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>14507900</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>12893100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17248600</v>
+      </c>
+      <c r="E47" s="3">
         <v>23100600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24130700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>22257100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>21668100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20627300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19215500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18987000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16333000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12790500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10241700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10664300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10658700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10793000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11135400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10941900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>10814900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9350500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9778700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11016200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>15050500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>15110400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>11090200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12402000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>10640900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>11466300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11236500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12897200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13409200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12935500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12308400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>11558300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>9073400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8544100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8868800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7409100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7222500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7112800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7040300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>5997400</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6927600</v>
+      </c>
+      <c r="E48" s="3">
         <v>5132100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4988400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4750800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6021700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5773300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5617100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5757900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5514500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5380400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5473400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5069900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4792700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4827100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4841000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4839600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4703000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4681200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4845500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4436900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4109300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3926000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3801800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3913900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3572900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3856500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3948500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4084700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4030500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2989500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2600100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2266900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2101600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1960800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1851400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1789500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1727600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1620800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1642500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1626200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7043900</v>
+      </c>
+      <c r="E49" s="3">
         <v>6856200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6667800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6627900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6640700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6437300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4149600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4304900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4171200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4207300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4292000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4192400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4152200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4436200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6143100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6067200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6036500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5977300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5868800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5865800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5725400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5452700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5186700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5167700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3852400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3978800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4024600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4376500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4212100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4258400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4025300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3608600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3254300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3128400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3157100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3072800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3079100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3034700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2794300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2829000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4065900</v>
+      </c>
+      <c r="E52" s="3">
         <v>4681800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3299900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3758800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4270600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3213900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3637200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3459000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3099500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2737800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2701900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2852300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2861000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2811100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2992300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3035800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2858400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2654000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2527600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2699000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2309700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2471100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>713000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>653000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1447200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1635400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1693800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1738600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1770100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2802500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1757400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1510300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1403200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1099600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1046600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>846100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>745300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>695600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>482800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>643400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>69180900</v>
+      </c>
+      <c r="E54" s="3">
         <v>65179100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>64216700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62376700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62895300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62562100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>58607200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>59493300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57180800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57433300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57363500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56332300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>56026600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58373500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>55119400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>53748800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>53539200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>51867400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>52475100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>54636200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>55909400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>54482000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>46313000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>45961800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44866400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>46814100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>46396600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>47249000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>47147100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46998400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>43215500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>38536000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>41368200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>38663100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>37359000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>36131300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>32970800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29833200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>26467900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>23989200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6162100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6007900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>496100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5149700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5333500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5342800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>732600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5559900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5227500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5088200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>278000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5096100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4970300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4955900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5359200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5345300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4974600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4928500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5714300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5751500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5497200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5156200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5110900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4613400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4713500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4859600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5035300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5475000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5463100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5149000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5138400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4722700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4397400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3905800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4084700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3708000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3318400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3220400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4167200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3046900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5006500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4193200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4556100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4350300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4417900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3016700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3070000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3259000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3662800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3579300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3130500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3286700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3427700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3604600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2897400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3584100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3220400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2057300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2026300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2167800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1251900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2081800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2115100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1651600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1639400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1350500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1320200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1439800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1453200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1577900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1452400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1125100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1989100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>958000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6862500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>8547500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7376600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>5542200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1424500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>573100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1950600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1955500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4919700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2160200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2131300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2232900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5233500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2362100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2223800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2125600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5092600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2800600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2729200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2804700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2969600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2811100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2398400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2429800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2544700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2587700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2557200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2368700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2293200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2735300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2554800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2559600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2479800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2407500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2174100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1981100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1665900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1515900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5264400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7103300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1230900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1238300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1154800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1051400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1113000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1068600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13119200</v>
+      </c>
+      <c r="E60" s="3">
         <v>12156600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12342400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11660300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11882700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10592400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11090800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11181000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11114100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10793000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10781600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11183400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11127200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11365200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11226200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11740600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10593300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9415500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10285300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10507000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9306300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9606700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9519200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9000300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8907600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8769700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8835400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9322400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9090400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8708000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8256800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7363700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>11650900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>11967100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>12178100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13493900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>11849800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>9814000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>6704600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4688600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11613600</v>
+      </c>
+      <c r="E61" s="3">
         <v>9454900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9323200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9308100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8402500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11046900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7797700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7769000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7731400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8801700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8799600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8704300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9156700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10141800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8907500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8506600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8985400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9490000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9444800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10501600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10526100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8799700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8398600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8302100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8732800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9280600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8960300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9265100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8655000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9213000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7973600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5767900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5791700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6298200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5314900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5433100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5042400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4981800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5013100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5201300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E62" s="3">
         <v>287900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>284100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>318400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>319000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>277700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>221000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>216400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>260600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>266600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>267500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>263300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>309100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>314700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1459800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1615400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1883400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1862100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1821700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1706200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1704800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1733800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1690600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1839500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1910100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2021300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1991000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2249200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2175700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2100500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1460700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1213200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>726600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>500600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>517500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>537200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>551500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>537600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>535500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>521300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25738300</v>
+      </c>
+      <c r="E66" s="3">
         <v>22793800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22794100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21979000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21309500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22587700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19751500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19691400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19621700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20349600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20329000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20601900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21078600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22332000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23613400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23735500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23356200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22571000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23276800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24588800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23033800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21476100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20881700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20218000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20624400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21287600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21205700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22584000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21827100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22076900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19558000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16185800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19978200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>20799300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>20240500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>19953600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>18328500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>16146100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>13048500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>11153700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,19 +7938,22 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="3">
+        <v>26145200</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25405200</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>16</v>
@@ -7787,11 +7961,11 @@
       <c r="H72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="3">
         <v>24670600</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>16</v>
@@ -7799,11 +7973,11 @@
       <c r="L72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N72" s="3">
         <v>22739000</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
@@ -7811,11 +7985,11 @@
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R72" s="3">
         <v>20913100</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
@@ -7823,11 +7997,11 @@
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V72" s="3">
         <v>20043700</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
@@ -7835,62 +8009,65 @@
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z72" s="3">
         <v>18831500</v>
       </c>
-      <c r="Z72" s="3" t="s">
+      <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18331300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19525200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19442700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18877400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19754000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19608700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18770400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17803100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16946900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15843800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15186500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14541100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13292200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>12592400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>12468300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>11891100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40005900</v>
+      </c>
+      <c r="E76" s="3">
         <v>38983700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38077600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37157000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>38395400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37173200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>36116800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37016000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34783600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34347600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34357600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>33224700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32492200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>33496600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>31505900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30013300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>30183000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29296400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>29198300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30047400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32875600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>33005900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>25431300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>25743800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24242000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25526500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25191000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24665000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25320100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24921500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23657500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22350200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>21390000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17863800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17118500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>16177700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14642300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>13687100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>13419300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>12835500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>341400</v>
+      </c>
+      <c r="E81" s="3">
         <v>499500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>254800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1577700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1022100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1063500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>711300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1088000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>755200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>754500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>366500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>915600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>718400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>848000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>615000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>505600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-122200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>188500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2353900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-83700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3684300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>714400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1997400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>520600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>965100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-994300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>368500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-49700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>283300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1734900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>918600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>960500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>620000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1179700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>655200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>258400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>519400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>451200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,43 +8990,44 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-272200</v>
+      </c>
+      <c r="E83" s="3">
         <v>258500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>261300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>245100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>226600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>217600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>521700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>261600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>245700</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>939100</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>16</v>
@@ -8836,8 +9035,8 @@
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8881,14 +9080,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>644400</v>
-      </c>
-      <c r="AH83" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>16</v>
@@ -8896,8 +9095,8 @@
       <c r="AJ83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK83" s="3">
-        <v>0</v>
+      <c r="AK83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL83" s="3">
         <v>0</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,103 +9738,106 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>505800</v>
+      </c>
+      <c r="E89" s="3">
         <v>387100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>373000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>176400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-122400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-827000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>322800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>610000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1153000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>861400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1497400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1305400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1466000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>850200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1107100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1207400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1071300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>258500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>650900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>476900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1139800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>591300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>839000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1137100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1206700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>344000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1698600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1373000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1064100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>252700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1297900</v>
-      </c>
-      <c r="AH89" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>16</v>
@@ -9628,8 +9845,8 @@
       <c r="AJ89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK89" s="3">
-        <v>0</v>
+      <c r="AK89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL89" s="3">
         <v>0</v>
@@ -9646,8 +9863,11 @@
       <c r="AP89" s="3">
         <v>0</v>
       </c>
+      <c r="AQ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,53 +9910,54 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1676800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-857700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-281900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-477700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-530400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-399600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-319600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-234500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-291500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-282300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-516200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-483600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-373100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-188500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -9761,32 +9982,32 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-125800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-85300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-136100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-189100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-207600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-452300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-900</v>
-      </c>
-      <c r="AH91" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>16</v>
@@ -9794,26 +10015,29 @@
       <c r="AJ91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-176500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-192500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-167000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-169800</v>
-      </c>
-      <c r="AO91" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AP91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AQ91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,88 +10283,91 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3895700</v>
+      </c>
+      <c r="E94" s="3">
         <v>716500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2628700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>420800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1192200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-166100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-772300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1990600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1948700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-431500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1866600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1562400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>949800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4753000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-750400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1106700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-511600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-407500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>282600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1986100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1746700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1056600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-127400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-910200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1136100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1987400</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>16</v>
@@ -10148,11 +10378,11 @@
       <c r="AF94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1678600</v>
-      </c>
-      <c r="AH94" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>16</v>
@@ -10160,8 +10390,8 @@
       <c r="AJ94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK94" s="3">
-        <v>0</v>
+      <c r="AK94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL94" s="3">
         <v>0</v>
@@ -10178,8 +10408,11 @@
       <c r="AP94" s="3">
         <v>0</v>
       </c>
+      <c r="AQ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,88 +10953,91 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2562300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-237000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>159100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>657800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1277700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2824900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-228800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-769700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1249100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>330600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1072900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-683100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-335100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-318900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-839000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>75500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>193600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1367100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1224100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>869900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2675500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1750700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-605900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-204500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-215300</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>16</v>
@@ -10802,11 +11048,11 @@
       <c r="AF100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH100" s="3">
         <v>2469900</v>
-      </c>
-      <c r="AH100" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>16</v>
@@ -10814,8 +11060,8 @@
       <c r="AJ100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
+      <c r="AK100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL100" s="3">
         <v>0</v>
@@ -10832,88 +11078,91 @@
       <c r="AP100" s="3">
         <v>0</v>
       </c>
+      <c r="AQ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>88100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-114800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>23400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-55700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>21700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>86000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-15300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-207200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>286700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>194800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-201500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>281800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>181400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-25800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-91500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-9700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-62300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>31900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-33500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>31800</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>16</v>
@@ -10924,11 +11173,11 @@
       <c r="AF101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-50700</v>
-      </c>
-      <c r="AH101" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>16</v>
@@ -10936,8 +11185,8 @@
       <c r="AJ101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
+      <c r="AK101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL101" s="3">
         <v>0</v>
@@ -10954,88 +11203,91 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-859400</v>
+      </c>
+      <c r="E102" s="3">
         <v>826500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2140100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1226700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2625600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1831000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-590200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2265000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1864800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>783900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1497800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-918400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2602800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4253200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-163700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1756800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>816600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-525100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-294800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2242100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2428800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-406700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-131600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1826900</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AD102" s="3" t="s">
         <v>16</v>
@@ -11046,11 +11298,11 @@
       <c r="AF102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH102" s="3">
         <v>2038600</v>
-      </c>
-      <c r="AH102" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AI102" s="3" t="s">
         <v>16</v>
@@ -11058,8 +11310,8 @@
       <c r="AJ102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AK102" s="3">
-        <v>0</v>
+      <c r="AK102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AL102" s="3">
         <v>0</v>
@@ -11074,6 +11326,9 @@
         <v>0</v>
       </c>
       <c r="AP102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="3">
         <v>0</v>
       </c>
     </row>
